--- a/outputs/daily/hr_rankings_2026-08-20.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-20.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2967,27 +2967,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>682829</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-20T16:40:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3030,26 +3030,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>55.2</v>
+        <v>62.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>53.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>70.8</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>10.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3131,112 +3131,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>50.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>93.03</t>
+          <t>92.68</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>104.0011</t>
+          <t>105.2173</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4541</t>
+          <t>0.4989</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1919</t>
+          <t>0.2341</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3465</t>
+          <t>0.3593</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>53.84</t>
+          <t>85.39</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.12</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.2647</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4801</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -3247,27 +3247,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>682829</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T16:40:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3310,26 +3310,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>62.9</v>
+        <v>55.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>66.09999999999999</v>
+        <v>53.4</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>70.8</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>10.8</v>
+        <v>6</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3411,112 +3411,112 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>50.49</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>92.68</t>
+          <t>93.03</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>105.2173</t>
+          <t>104.0011</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4989</t>
+          <t>0.4541</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2341</t>
+          <t>0.1919</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3593</t>
+          <t>0.3465</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>75.38</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>85.39</t>
+          <t>53.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>34.12</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2647</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.5133</t>
+          <t>0.4801</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>60.9</v>
+        <v>61.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>30.3</v>
+        <v>34.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3937,12 +3937,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/17, 1 HR</t>
+          <t>Last 7 games: 1/18, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>75.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6177,12 +6177,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>80</v>
       </c>
       <c r="U25" t="n">
-        <v>24</v>
+        <v>22.4</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8921,7 +8921,7 @@
         <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>22.8</v>
+        <v>21.8</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 1 HR</t>
+          <t>Last 7 games: 3/21, 1 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>80</v>
       </c>
       <c r="U55" t="n">
-        <v>24.9</v>
+        <v>22.9</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
@@ -15799,47 +15799,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>663662</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Daz Cameron</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -15848,7 +15848,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15862,26 +15862,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>31.4</v>
+        <v>45.9</v>
       </c>
       <c r="Q56" t="n">
-        <v>41.5</v>
+        <v>40.5</v>
       </c>
       <c r="R56" t="n">
-        <v>41.1</v>
+        <v>50.1</v>
       </c>
       <c r="S56" t="n">
-        <v>100</v>
+        <v>76.2</v>
       </c>
       <c r="T56" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U56" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -15916,7 +15916,7 @@
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -15928,17 +15928,17 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -15948,12 +15948,12 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 3 games: 2/7, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -15963,112 +15963,112 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>87.35</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>98.1234</t>
+          <t>103.328</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.3144</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1035</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.2266</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1463</t>
+          <t>0.1838</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.3893</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16079,22 +16079,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -16104,27 +16104,27 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -16142,26 +16142,26 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>45.9</v>
+        <v>37.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>40.5</v>
+        <v>41.2</v>
       </c>
       <c r="R57" t="n">
-        <v>50.1</v>
+        <v>36.1</v>
       </c>
       <c r="S57" t="n">
-        <v>76.2</v>
+        <v>93.2</v>
       </c>
       <c r="T57" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U57" t="n">
-        <v>22.4</v>
+        <v>14.1</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -16196,7 +16196,7 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -16213,12 +16213,12 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -16228,12 +16228,12 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -16243,112 +16243,112 @@
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>43.83</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>103.328</t>
+          <t>100.4496</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.174</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.3346</t>
+          <t>0.3406</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.1838</t>
+          <t>0.1694</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1458</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -16359,47 +16359,47 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-21T00:10:00Z</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -16422,61 +16422,65 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>37.6</v>
+        <v>41.9</v>
       </c>
       <c r="Q58" t="n">
-        <v>41.2</v>
+        <v>63.7</v>
       </c>
       <c r="R58" t="n">
-        <v>36.1</v>
+        <v>27.6</v>
       </c>
       <c r="S58" t="n">
-        <v>93.2</v>
+        <v>71.7</v>
       </c>
       <c r="T58" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U58" t="n">
-        <v>14.1</v>
+        <v>18.3</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -16493,27 +16497,27 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -16523,112 +16527,104 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>89.78</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>100.4496</t>
+          <t>101.4918</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4007</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.1736</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>0.3406</t>
+          <t>0.3063</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>43.76</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.1694</t>
+          <t>0.2019</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.505</t>
         </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>0.1458</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="BG58" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH58" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="BG58" t="inlineStr"/>
+      <c r="BH58" t="inlineStr"/>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr"/>
@@ -16639,12 +16635,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -16669,7 +16665,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -16702,11 +16698,11 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="Q59" t="n">
         <v>63.7</v>
@@ -16715,13 +16711,13 @@
         <v>27.6</v>
       </c>
       <c r="S59" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U59" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16735,7 +16731,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -16777,27 +16773,27 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 1/21, 0 HR</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -16807,67 +16803,67 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>101.4918</t>
+          <t>100.835</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.4007</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.1736</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.3063</t>
+          <t>0.2927</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>75.72</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>30.37</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.2019</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
@@ -16915,47 +16911,47 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>596142</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Gary Sánchez</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-21T00:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16964,7 +16960,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -16978,65 +16974,61 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>41.4</v>
+        <v>42.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>63.7</v>
+        <v>41.2</v>
       </c>
       <c r="R60" t="n">
-        <v>27.6</v>
+        <v>36.1</v>
       </c>
       <c r="S60" t="n">
-        <v>59.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T60" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr"/>
@@ -17053,27 +17045,27 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/21, 0 HR</t>
+          <t>Last 7 games: 4/20, 1 HR</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
@@ -17083,104 +17075,112 @@
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>100.835</t>
+          <t>101.2803</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.4287</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>0.2927</t>
+          <t>0.3465</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>30.37</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.2143</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD60" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>0.1458</t>
         </is>
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>27.3</t>
-        </is>
-      </c>
-      <c r="BG60" t="inlineStr"/>
-      <c r="BH60" t="inlineStr"/>
+          <t>25.22</t>
+        </is>
+      </c>
+      <c r="BG60" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH60" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr"/>
@@ -17191,56 +17191,56 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>663662</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gary Sánchez</t>
+          <t>Daz Cameron</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -17254,26 +17254,26 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>42.2</v>
+        <v>31.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>41.2</v>
+        <v>41.5</v>
       </c>
       <c r="R61" t="n">
-        <v>36.1</v>
+        <v>41.1</v>
       </c>
       <c r="S61" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T61" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U61" t="n">
-        <v>30.3</v>
+        <v>19.5</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -17320,32 +17320,32 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 1 HR</t>
+          <t>Last 3 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
@@ -17355,112 +17355,112 @@
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>87.35</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>98.1234</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>0.4287</t>
+          <t>0.3144</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1035</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>0.3465</t>
+          <t>0.2266</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>0.2143</t>
+          <t>0.1463</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD61" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.3893</t>
         </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
-          <t>0.1458</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ61" t="inlineStr"/>
@@ -17471,56 +17471,56 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>669394</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -17534,58 +17534,62 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>36.2</v>
+        <v>48.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>66.09999999999999</v>
+        <v>22.5</v>
       </c>
       <c r="R62" t="n">
-        <v>41.1</v>
+        <v>27.6</v>
       </c>
       <c r="S62" t="n">
-        <v>52.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T62" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U62" t="n">
-        <v>50.3</v>
+        <v>57.6</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17605,27 +17609,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Contact streak: 2/6 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 2.4 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
@@ -17635,112 +17639,104 @@
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>100.3908</t>
+          <t>102.6757</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.3894</t>
+          <t>0.4227</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1872</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.2886</t>
+          <t>0.3086</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>75.37</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>58.14</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>41.88</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>31.19</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.1359</t>
+          <t>0.1844</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>89.25</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.5133</t>
+          <t>0.3542</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1095</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>26.03</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH62" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="BG62" t="inlineStr"/>
+      <c r="BH62" t="inlineStr"/>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -17751,32 +17747,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>669394</t>
+          <t>680869</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Zack Gelof</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-21T00:05:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -17786,21 +17782,21 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17814,62 +17810,58 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>48.5</v>
+        <v>37.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>22.5</v>
+        <v>32.7</v>
       </c>
       <c r="R63" t="n">
-        <v>27.6</v>
+        <v>48.2</v>
       </c>
       <c r="S63" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T63" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U63" t="n">
-        <v>57.6</v>
+        <v>54.7</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17889,12 +17881,12 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -17909,7 +17901,7 @@
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.5% barrel, 2.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
@@ -17919,104 +17911,112 @@
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>43.14</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>102.6757</t>
+          <t>99.6651</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.4227</t>
+          <t>0.3718</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.1872</t>
+          <t>0.1683</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.3086</t>
+          <t>0.2785</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>75.37</t>
+          <t>73.29</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>58.14</t>
+          <t>28.06</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>41.88</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>27.17</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.1844</t>
+          <t>0.1799</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>89.25</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.3542</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.1095</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="BG63" t="inlineStr"/>
-      <c r="BH63" t="inlineStr"/>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="BG63" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH63" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -18027,47 +18027,47 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>680869</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Zack Gelof</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>48.2</v>
+        <v>48</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18090,26 +18090,26 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>37.5</v>
+        <v>36.2</v>
       </c>
       <c r="Q64" t="n">
-        <v>32.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R64" t="n">
-        <v>48.2</v>
+        <v>41.1</v>
       </c>
       <c r="S64" t="n">
-        <v>96.59999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="T64" t="n">
         <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>54.7</v>
+        <v>43.2</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -18161,27 +18161,27 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/7, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
@@ -18191,112 +18191,112 @@
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>99.6651</t>
+          <t>100.3908</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.3718</t>
+          <t>0.3894</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.2785</t>
+          <t>0.2886</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>73.29</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>31.19</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.1799</t>
+          <t>0.1359</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -18945,7 +18945,7 @@
         <v>50</v>
       </c>
       <c r="U67" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
@@ -19168,7 +19168,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -21169,7 +21169,7 @@
         <v>80</v>
       </c>
       <c r="U75" t="n">
-        <v>37.8</v>
+        <v>36</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Contact streak: 9/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
@@ -21927,27 +21927,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>663647</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T16:40:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -21957,17 +21957,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Landen Roupp</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>694738</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -21976,7 +21976,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -21990,26 +21990,26 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>38.8</v>
+        <v>31.6</v>
       </c>
       <c r="Q78" t="n">
-        <v>23.2</v>
+        <v>55.1</v>
       </c>
       <c r="R78" t="n">
-        <v>39.6</v>
+        <v>70.8</v>
       </c>
       <c r="S78" t="n">
-        <v>94.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T78" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U78" t="n">
-        <v>36</v>
+        <v>30.3</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -22061,12 +22061,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -22076,12 +22076,12 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 2/10, 1 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22091,112 +22091,112 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>90.07</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>101.2217</t>
+          <t>99.7622</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.3826</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1716</t>
+          <t>0.1397</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>27.08</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1978</t>
+          <t>0.0948</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.3639</t>
+          <t>0.4801</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -22207,27 +22207,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>663647</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-20T16:40:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -22237,17 +22237,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Landen Roupp</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>694738</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -22270,26 +22270,26 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>31.6</v>
+        <v>38.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>55.1</v>
+        <v>23.2</v>
       </c>
       <c r="R79" t="n">
-        <v>70.8</v>
+        <v>39.6</v>
       </c>
       <c r="S79" t="n">
-        <v>44.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T79" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U79" t="n">
-        <v>30.3</v>
+        <v>34.4</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -22341,12 +22341,12 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -22356,12 +22356,12 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/10, 1 HR</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -22371,112 +22371,112 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>90.07</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>99.7622</t>
+          <t>101.2217</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.3826</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.1397</t>
+          <t>0.1716</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>35.59</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>27.08</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.0948</t>
+          <t>0.1978</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.4801</t>
+          <t>0.3639</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr"/>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -23900,7 +23900,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -24711,47 +24711,47 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>694197</t>
+          <t>681297</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Angel Genao</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T22:35:00Z</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Landen Roupp</t>
+          <t>Gerrit Cole</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>694738</t>
+          <t>543037</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24774,61 +24774,65 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>41.1</v>
+        <v>45.9</v>
       </c>
       <c r="Q88" t="n">
-        <v>22.1</v>
+        <v>41</v>
       </c>
       <c r="R88" t="n">
-        <v>39.6</v>
+        <v>32.1</v>
       </c>
       <c r="S88" t="n">
-        <v>86.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T88" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U88" t="n">
-        <v>27.7</v>
+        <v>48.7</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr"/>
@@ -24845,142 +24849,134 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>101.156</t>
+          <t>100.7389</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.425</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.2051</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.3126</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>74.44</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1561</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.3639</t>
+          <t>0.369</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>22.45</t>
-        </is>
-      </c>
-      <c r="BG88" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH88" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>30.1</t>
+        </is>
+      </c>
+      <c r="BG88" t="inlineStr"/>
+      <c r="BH88" t="inlineStr"/>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -24991,27 +24987,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>681297</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-20T22:35:00Z</t>
+          <t>2026-08-21T00:10:00Z</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -25021,17 +25017,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Gerrit Cole</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>543037</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -25054,26 +25050,26 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>45.9</v>
+        <v>46.3</v>
       </c>
       <c r="Q89" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="R89" t="n">
-        <v>32.1</v>
+        <v>27.6</v>
       </c>
       <c r="S89" t="n">
-        <v>40.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T89" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U89" t="n">
-        <v>48.7</v>
+        <v>18</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -25087,7 +25083,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -25129,27 +25125,27 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
@@ -25159,104 +25155,104 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>100.7389</t>
+          <t>100.102</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.4166</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>0.2051</t>
+          <t>0.2027</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>0.3126</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>74.44</t>
+          <t>71.26</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.96</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>0.1561</t>
+          <t>0.1946</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr"/>
       <c r="BH89" t="inlineStr"/>
       <c r="BI89" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ89" t="inlineStr"/>
@@ -25267,47 +25263,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>678545</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Osleivis Basabe</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-21T00:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -25316,7 +25312,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -25330,65 +25326,61 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>46.3</v>
+        <v>30.1</v>
       </c>
       <c r="Q90" t="n">
-        <v>32</v>
+        <v>56.1</v>
       </c>
       <c r="R90" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S90" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T90" t="n">
         <v>50</v>
       </c>
       <c r="U90" t="n">
-        <v>18</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr"/>
@@ -25405,12 +25397,12 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
@@ -25420,119 +25412,127 @@
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>100.102</t>
+          <t>98.4704</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.4166</t>
+          <t>0.361</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.2027</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.271</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.1946</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.4085</t>
         </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1796</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>33.9</t>
-        </is>
-      </c>
-      <c r="BG90" t="inlineStr"/>
-      <c r="BH90" t="inlineStr"/>
+          <t>25.58</t>
+        </is>
+      </c>
+      <c r="BG90" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25543,24 +25543,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>678545</t>
+          <t>694197</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Osleivis Basabe</t>
+          <t>Angel Genao</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>2026-08-20T17:10:00Z</t>
@@ -25573,17 +25573,17 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Landen Roupp</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>694738</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -25606,26 +25606,26 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>30.1</v>
+        <v>41.1</v>
       </c>
       <c r="Q91" t="n">
-        <v>56.1</v>
+        <v>22.1</v>
       </c>
       <c r="R91" t="n">
         <v>39.6</v>
       </c>
       <c r="S91" t="n">
-        <v>76.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T91" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U91" t="n">
-        <v>10.6</v>
+        <v>25.8</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -25677,12 +25677,12 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -25692,112 +25692,112 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>98.4704</t>
+          <t>101.156</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>0.425</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>90.19</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>0.4085</t>
+          <t>0.3639</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>0.1796</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG91" t="inlineStr">
@@ -25848,7 +25848,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -26379,47 +26379,47 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>643446</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -26442,26 +26442,26 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>14.9</v>
+        <v>13.4</v>
       </c>
       <c r="Q94" t="n">
-        <v>66.09999999999999</v>
+        <v>32.7</v>
       </c>
       <c r="R94" t="n">
-        <v>41.1</v>
+        <v>48.2</v>
       </c>
       <c r="S94" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="T94" t="n">
         <v>80</v>
       </c>
       <c r="U94" t="n">
-        <v>29.7</v>
+        <v>78.7</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
@@ -26513,27 +26513,27 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
@@ -26543,112 +26543,112 @@
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>32.62</t>
+          <t>32.06</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>86.92</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>96.9759</t>
+          <t>96.7559</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3796</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>0.1011</t>
+          <t>0.1048</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>0.3264</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="BD94" t="inlineStr">
         <is>
-          <t>0.5133</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="BG94" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI94" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ94" t="inlineStr"/>
@@ -26659,47 +26659,47 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>643446</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -26708,7 +26708,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26722,26 +26722,26 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>13.4</v>
+        <v>14.9</v>
       </c>
       <c r="Q95" t="n">
-        <v>32.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R95" t="n">
-        <v>48.2</v>
+        <v>41.1</v>
       </c>
       <c r="S95" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="T95" t="n">
         <v>80</v>
       </c>
       <c r="U95" t="n">
-        <v>78.7</v>
+        <v>27</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -26793,27 +26793,27 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26823,112 +26823,112 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>32.06</t>
+          <t>32.62</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>86.92</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>96.7559</t>
+          <t>96.9759</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.3796</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1048</t>
+          <t>0.1011</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3264</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -27520,7 +27520,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -28936,7 +28936,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>80</v>
       </c>
       <c r="U103" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
@@ -29216,7 +29216,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>75</v>
       </c>
       <c r="U104" t="n">
-        <v>32</v>
+        <v>29.7</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -29316,7 +29316,7 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 7/22, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
@@ -29447,47 +29447,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>661531</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Brian Serven</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -29496,7 +29496,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>43.1</v>
+        <v>42.6</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -29510,26 +29510,26 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>12.2</v>
+        <v>35</v>
       </c>
       <c r="Q105" t="n">
-        <v>66.09999999999999</v>
+        <v>32.7</v>
       </c>
       <c r="R105" t="n">
-        <v>41.1</v>
+        <v>48.2</v>
       </c>
       <c r="S105" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T105" t="n">
         <v>50</v>
       </c>
       <c r="U105" t="n">
-        <v>36.5</v>
+        <v>49.9</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -29564,7 +29564,7 @@
       <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr"/>
@@ -29581,142 +29581,142 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>85.32</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>97.3601</t>
+          <t>98.6823</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.3493</t>
+          <t>0.424</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.1019</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.298</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
+          <t>35.7</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>0.257</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>4.48</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>45.38</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>91.67</t>
+        </is>
+      </c>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>0.415</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr">
+        <is>
+          <t>0.1268</t>
+        </is>
+      </c>
+      <c r="BF105" t="inlineStr">
+        <is>
           <t>21.5</t>
         </is>
       </c>
-      <c r="AY105" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>0.1566</t>
-        </is>
-      </c>
-      <c r="BA105" t="inlineStr">
-        <is>
-          <t>11.74</t>
-        </is>
-      </c>
-      <c r="BB105" t="inlineStr">
-        <is>
-          <t>47.64</t>
-        </is>
-      </c>
-      <c r="BC105" t="inlineStr">
-        <is>
-          <t>91.1</t>
-        </is>
-      </c>
-      <c r="BD105" t="inlineStr">
-        <is>
-          <t>0.5133</t>
-        </is>
-      </c>
-      <c r="BE105" t="inlineStr">
-        <is>
-          <t>0.2278</t>
-        </is>
-      </c>
-      <c r="BF105" t="inlineStr">
-        <is>
-          <t>26.03</t>
-        </is>
-      </c>
       <c r="BG105" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -29727,22 +29727,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>661531</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brian Serven</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -29752,31 +29752,31 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -29790,26 +29790,26 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>35</v>
+        <v>17.1</v>
       </c>
       <c r="Q106" t="n">
-        <v>32.7</v>
+        <v>38.7</v>
       </c>
       <c r="R106" t="n">
-        <v>48.2</v>
+        <v>50.1</v>
       </c>
       <c r="S106" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T106" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U106" t="n">
-        <v>49.9</v>
+        <v>0</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -29844,7 +29844,7 @@
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr"/>
@@ -29861,142 +29861,142 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.08</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>98.6823</t>
+          <t>96.7345</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>0.3611</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.1272</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.2892</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>46.42</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.1572</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD106" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="BG106" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI106" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ106" t="inlineStr"/>
@@ -30007,56 +30007,56 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -30070,26 +30070,26 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>17.1</v>
+        <v>12.2</v>
       </c>
       <c r="Q107" t="n">
-        <v>38.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R107" t="n">
-        <v>50.1</v>
+        <v>41.1</v>
       </c>
       <c r="S107" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T107" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -30124,7 +30124,7 @@
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr"/>
@@ -30141,12 +30141,12 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -30156,12 +30156,12 @@
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
@@ -30171,112 +30171,112 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>87.08</t>
+          <t>85.32</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>96.7345</t>
+          <t>97.3601</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.3493</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>0.1272</t>
+          <t>0.1019</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>0.2892</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>72.89</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>46.42</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>0.1572</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD107" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BG107" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI107" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ107" t="inlineStr"/>
@@ -31391,52 +31391,52 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>806367</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turner Hill</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L112" t="n">
@@ -31454,26 +31454,26 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>13.1</v>
+        <v>24.4</v>
       </c>
       <c r="Q112" t="n">
-        <v>56.1</v>
+        <v>38.4</v>
       </c>
       <c r="R112" t="n">
-        <v>39.6</v>
+        <v>36.1</v>
       </c>
       <c r="S112" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T112" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U112" t="n">
-        <v>24.9</v>
+        <v>38.9</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -31508,7 +31508,7 @@
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr"/>
@@ -31520,17 +31520,17 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -31540,12 +31540,12 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Last 4 games: 2/7, 0 HR</t>
+          <t>Contact streak: 11/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -31555,112 +31555,112 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>96.3305</t>
+          <t>99.1983</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>0.4068</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>0.1331</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>37.19</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>90.19</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="BD112" t="inlineStr">
         <is>
-          <t>0.4085</t>
+          <t>0.4023</t>
         </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
-          <t>0.1796</t>
+          <t>0.1656</t>
         </is>
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>27.31</t>
         </is>
       </c>
       <c r="BG112" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI112" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ112" t="inlineStr"/>
@@ -31671,22 +31671,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>671976</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -31696,31 +31696,31 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Grant Holmes</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>656550</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -31734,26 +31734,26 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>24.4</v>
+        <v>11.2</v>
       </c>
       <c r="Q113" t="n">
-        <v>38.4</v>
+        <v>51.9</v>
       </c>
       <c r="R113" t="n">
-        <v>36.1</v>
+        <v>50.1</v>
       </c>
       <c r="S113" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T113" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U113" t="n">
-        <v>38.9</v>
+        <v>57.5</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -31805,27 +31805,27 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Contact streak: 11/29 over last 7 games</t>
+          <t>Contact streak: 8/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 18.1 HR allowed</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
@@ -31835,112 +31835,112 @@
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.01</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>99.1983</t>
+          <t>97.7553</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
         <is>
-          <t>0.4068</t>
+          <t>0.3159</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>0.1331</t>
+          <t>0.0952</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2586</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>42.26</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>0.1236</t>
+          <t>0.1085</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>37.19</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="BD113" t="inlineStr">
         <is>
-          <t>0.4023</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
-          <t>0.1656</t>
+          <t>0.1768</t>
         </is>
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI113" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ113" t="inlineStr"/>
@@ -31951,47 +31951,47 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>806367</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Turner Hill</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Grant Holmes</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>656550</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -32000,7 +32000,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -32018,22 +32018,22 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>11.2</v>
+        <v>13.1</v>
       </c>
       <c r="Q114" t="n">
-        <v>51.9</v>
+        <v>56.1</v>
       </c>
       <c r="R114" t="n">
-        <v>50.1</v>
+        <v>39.6</v>
       </c>
       <c r="S114" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T114" t="n">
         <v>80</v>
       </c>
       <c r="U114" t="n">
-        <v>57.5</v>
+        <v>19.5</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -32068,7 +32068,7 @@
       <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr"/>
@@ -32080,32 +32080,32 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Contact streak: 8/21 over last 7 games</t>
+          <t>Last 4 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 18.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -32115,112 +32115,112 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>87.01</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>97.7553</t>
+          <t>96.3305</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.3159</t>
+          <t>0.373</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.0952</t>
+          <t>0.102</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.2586</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>42.26</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.1085</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4085</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.1768</t>
+          <t>0.1796</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -32256,7 +32256,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -32869,7 +32869,7 @@
         <v>80</v>
       </c>
       <c r="U117" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -32936,7 +32936,7 @@
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Last 7 games: 3/23, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
@@ -33092,7 +33092,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -33372,7 +33372,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -33932,7 +33932,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -34764,7 +34764,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -35320,7 +35320,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -35600,7 +35600,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -35880,7 +35880,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -36460,7 +36460,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>75</v>
       </c>
       <c r="U130" t="n">
-        <v>15.3</v>
+        <v>13.6</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
@@ -36716,7 +36716,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -37020,7 +37020,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>80</v>
       </c>
       <c r="U132" t="n">
-        <v>17.7</v>
+        <v>16.1</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -37120,7 +37120,7 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
@@ -37390,7 +37390,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
@@ -37400,7 +37400,7 @@
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/10, 0 HR</t>
+          <t>Last 7 games: 1/11, 0 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
@@ -37556,7 +37556,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -38116,7 +38116,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -38696,7 +38696,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -38729,7 +38729,7 @@
         <v>50</v>
       </c>
       <c r="U138" t="n">
-        <v>24.9</v>
+        <v>22.9</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
@@ -39232,7 +39232,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -40620,7 +40620,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -41456,7 +41456,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -42568,7 +42568,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -43980,7 +43980,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>75</v>
       </c>
       <c r="U157" t="n">
-        <v>36</v>
+        <v>34.4</v>
       </c>
       <c r="V157" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
@@ -44080,7 +44080,7 @@
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
@@ -44293,7 +44293,7 @@
         <v>50</v>
       </c>
       <c r="U158" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="V158" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
@@ -44360,7 +44360,7 @@
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL158" t="inlineStr">
@@ -45072,7 +45072,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -46510,7 +46510,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -48206,7 +48206,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -48306,7 +48306,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -48437,27 +48437,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>682829</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-20T16:40:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -48467,17 +48467,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -48500,26 +48500,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>55.2</v>
+        <v>62.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>53.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>70.8</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>10.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -48533,7 +48533,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -48571,12 +48571,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -48586,12 +48586,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -48601,112 +48601,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>50.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>93.03</t>
+          <t>92.68</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>104.0011</t>
+          <t>105.2173</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4541</t>
+          <t>0.4989</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1919</t>
+          <t>0.2341</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3465</t>
+          <t>0.3593</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>53.84</t>
+          <t>85.39</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.12</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.2647</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4801</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -48717,27 +48717,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>682829</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T16:40:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -48747,17 +48747,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -48766,7 +48766,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -48780,26 +48780,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>62.9</v>
+        <v>55.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>66.09999999999999</v>
+        <v>53.4</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>70.8</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>10.8</v>
+        <v>6</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -48866,12 +48866,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -48881,112 +48881,112 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>50.49</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>92.68</t>
+          <t>93.03</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>105.2173</t>
+          <t>104.0011</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4989</t>
+          <t>0.4541</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2341</t>
+          <t>0.1919</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3593</t>
+          <t>0.3465</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>75.38</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>85.39</t>
+          <t>53.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>34.12</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2647</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.5133</t>
+          <t>0.4801</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -49322,7 +49322,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>60.9</v>
+        <v>61.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>30.3</v>
+        <v>34.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -49407,12 +49407,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -49422,7 +49422,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -49578,7 +49578,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -50252,7 +50252,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -50262,7 +50262,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/17, 1 HR</t>
+          <t>Last 7 games: 1/18, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -50418,7 +50418,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -50698,7 +50698,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -50978,7 +50978,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -51562,7 +51562,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -51595,7 +51595,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>75.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -51647,12 +51647,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-20.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-20.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>63.7</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>32</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>63.7</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>76.2</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>63.7</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>63.7</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S11" t="n">
         <v>64.3</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>63.7</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S15" t="n">
         <v>96.59999999999999</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>94.90000000000001</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>63.7</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -6128,7 +6128,7 @@
         <v>63.7</v>
       </c>
       <c r="R21" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S21" t="n">
         <v>94.90000000000001</v>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -6408,7 +6408,7 @@
         <v>32</v>
       </c>
       <c r="R22" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S22" t="n">
         <v>64.3</v>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>32</v>
       </c>
       <c r="R24" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S24" t="n">
         <v>86.40000000000001</v>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>32</v>
       </c>
       <c r="R26" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S26" t="n">
         <v>96.59999999999999</v>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>32</v>
       </c>
       <c r="R27" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S27" t="n">
         <v>93.2</v>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -8088,7 +8088,7 @@
         <v>32</v>
       </c>
       <c r="R28" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S28" t="n">
         <v>76.2</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8648,7 +8648,7 @@
         <v>63.7</v>
       </c>
       <c r="R30" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S30" t="n">
         <v>44.8</v>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>63.7</v>
       </c>
       <c r="R31" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S31" t="n">
         <v>52.4</v>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>32</v>
       </c>
       <c r="R35" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S35" t="n">
         <v>44.8</v>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>30.7</v>
       </c>
       <c r="R36" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S36" t="n">
         <v>52.4</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>63.7</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>32</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -12870,7 +12870,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>63.7</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>76.2</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>63.7</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>63.7</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S11" t="n">
         <v>64.3</v>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -14830,7 +14830,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>63.7</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S15" t="n">
         <v>96.59999999999999</v>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>94.90000000000001</v>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>63.7</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -16534,7 +16534,7 @@
         <v>63.7</v>
       </c>
       <c r="R21" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S21" t="n">
         <v>94.90000000000001</v>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-20.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-20.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
